--- a/sku-import-130-raw.xlsx
+++ b/sku-import-130-raw.xlsx
@@ -587,6 +587,35 @@
     <col min="9" max="9" width="28.0" customWidth="true"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" t="s">
         <v>9</v>
